--- a/АБК/Том СПС АБК/Протокол сопротивления изоляции СПС АБК (образец и бланк).xlsx
+++ b/АБК/Том СПС АБК/Протокол сопротивления изоляции СПС АБК (образец и бланк).xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Исполнительная документация: 16/1/26-ИД-АБК, листы 2–3; кабельный журнал 16/1/26-ИД-АБК.КЖ (раздел СПС). Рабочая документация 16/1/26-АПС,СОУЭ-Р.</t>
+          <t>Исполнительная документация: 16/1/26-АПС,СОУЭ-ИД-АБК, листы 2–3; кабельный журнал 16/1/26-АПС,СОУЭ-ИД-АБК.КЖ. Рабочая документация 16/1/26-АПС,СОУЭ-Р.</t>
         </is>
       </c>
     </row>
@@ -2201,17 +2201,17 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>ДПЛС2.1</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>AU2</t>
+          <t>2BTH1.18,(40)</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>BIAD42\1.5Вт</t>
+          <t>2BTH1.25(60)</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -2221,28 +2221,28 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>1x2x1</t>
+          <t>1x2x0,5</t>
         </is>
       </c>
       <c r="G45" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>&gt; 2,00 ГОм</t>
+          <t>&gt; 999</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>&gt; 2,00 ГОм</t>
+          <t>&gt; 999</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
@@ -2257,17 +2257,17 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>ДПЛС2.1</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>BIAD42\1.5Вт</t>
+          <t>2BTH1.25(60)</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>BIAD41\3Вт</t>
+          <t>2BTH1.26(60)</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -2277,28 +2277,28 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>1x2x1</t>
+          <t>1x2x0,5</t>
         </is>
       </c>
       <c r="G46" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>&gt; 2,00 ГОм</t>
+          <t>&gt; 999</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>&gt; 2,00 ГОм</t>
+          <t>&gt; 999</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -2313,17 +2313,17 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>ДПЛС2.1</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>BIAD41\3Вт</t>
+          <t>2BTH1.25(60)</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>BIAD38\1.5Вт</t>
+          <t>2BTH1.27(60)</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
@@ -2333,28 +2333,28 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>1x2x1</t>
+          <t>1x2x0,5</t>
         </is>
       </c>
       <c r="G47" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>&gt; 2,00 ГОм</t>
+          <t>&gt; 999</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>&gt; 2,00 ГОм</t>
+          <t>&gt; 999</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
@@ -2369,17 +2369,17 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>ДПЛС2.1</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>BIAD38\1.5Вт</t>
+          <t>2BTH1.27(60)</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>BIAD43\1.5Вт</t>
+          <t>2BTH1.19,(40)</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -2389,28 +2389,28 @@
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>1x2x1</t>
+          <t>1x2x0,5</t>
         </is>
       </c>
       <c r="G48" s="9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>&gt; 2,00 ГОм</t>
+          <t>&gt; 999</t>
         </is>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>&gt; 2,00 ГОм</t>
+          <t>&gt; 999</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>BIAD43\1.5Вт</t>
+          <t>AU2</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>BIAD44\1.5Вт</t>
+          <t>BIAD42\1.5Вт</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="G49" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H49" s="9" t="n">
         <v>500</v>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>BIAD44\1.5Вт</t>
+          <t>BIAD42\1.5Вт</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>BIAD39\3Вт</t>
+          <t>BIAD41\3Вт</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="G50" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H50" s="9" t="n">
         <v>500</v>
@@ -2540,12 +2540,12 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>BIAD39\3Вт</t>
+          <t>BIAD41\3Вт</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>BIAD45\1.5Вт</t>
+          <t>BIAD38\1.5Вт</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H51" s="9" t="n">
         <v>500</v>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>BIAD45\1.5Вт</t>
+          <t>BIAD38\1.5Вт</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>BIAD46\1.5Вт</t>
+          <t>BIAD43\1.5Вт</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="G52" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H52" s="9" t="n">
         <v>500</v>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>BIAD46\1.5Вт</t>
+          <t>BIAD43\1.5Вт</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>BIAD40\3Вт</t>
+          <t>BIAD44\1.5Вт</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H53" s="9" t="n">
         <v>500</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>BIAD40\3Вт</t>
+          <t>BIAD44\1.5Вт</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>BIAD47\1.5Вт</t>
+          <t>BIAD39\3Вт</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="G54" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H54" s="9" t="n">
         <v>500</v>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>BIAD47\1.5Вт</t>
+          <t>BIAD39\3Вт</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>BIAD48\1.5Вт</t>
+          <t>BIAD45\1.5Вт</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>BIAD48\1.5Вт</t>
+          <t>BIAD45\1.5Вт</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>BIAD49\1.5Вт</t>
+          <t>BIAD46\1.5Вт</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>BIAD49\1.5Вт</t>
+          <t>BIAD46\1.5Вт</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>BIAD50\1.5Вт</t>
+          <t>BIAD40\3Вт</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="G57" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H57" s="9" t="n">
         <v>500</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>BIAD50\1.5Вт</t>
+          <t>BIAD40\3Вт</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>BIAD51\1.5Вт</t>
+          <t>BIAD47\1.5Вт</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>BIAD51\1.5Вт</t>
+          <t>BIAD47\1.5Вт</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>BIAD52\1.5Вт</t>
+          <t>BIAD48\1.5Вт</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="G59" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>500</v>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>BIAD52\1.5Вт</t>
+          <t>BIAD48\1.5Вт</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>BIAD53\1.5Вт</t>
+          <t>BIAD49\1.5Вт</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="G60" s="9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H60" s="9" t="n">
         <v>500</v>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>BIAD53\1.5Вт</t>
+          <t>BIAD49\1.5Вт</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>BIAD54\1.5Вт</t>
+          <t>BIAD50\1.5Вт</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>BIAD54\1.5Вт</t>
+          <t>BIAD50\1.5Вт</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>ST2</t>
+          <t>BIAD51\1.5Вт</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="G62" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H62" s="9" t="n">
         <v>500</v>
@@ -3195,123 +3195,345 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>BIAD51\1.5Вт</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>BIAD52\1.5Вт</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>КПСнг(А)–FRHF</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>1x2x1</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>&gt; 2,00 ГОм</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>&gt; 2,00 ГОм</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>соответствует</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>BIAD52\1.5Вт</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>BIAD53\1.5Вт</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>КПСнг(А)–FRHF</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>1x2x1</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I64" s="9" t="n">
+        <v>910</v>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>&gt; 2,00 ГОм</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>соответствует</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>BIAD53\1.5Вт</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>BIAD54\1.5Вт</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>КПСнг(А)–FRHF</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>1x2x1</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>&gt; 2,00 ГОм</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>&gt; 2,00 ГОм</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>соответствует</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>BIAD54\1.5Вт</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>ST2</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>КПСнг(А)–FRHF</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>1x2x1</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>&gt; 2,00 ГОм</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>&gt; 2,00 ГОм</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>соответствует</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
           <t>AU2</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>UR3</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>AU2</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>UTP-4P-Cat.5e</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>4х2х0.52</t>
         </is>
       </c>
-      <c r="G63" s="9" t="n">
+      <c r="G67" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="H63" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="H67" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="J63" s="9" t="inlineStr">
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>&gt; 999</t>
         </is>
       </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="L63" s="9" t="inlineStr">
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
         <is>
           <t>соответствует</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>Заключение: Сопротивление изоляции всех испытанных кабельных линий соответствует требованиям ГОСТ Р 50571.16-2019 и ПУЭ п. 1.8.37. Линии пригодны к эксплуатации.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>Протокол распространяется только на испытанные линии. Запись «&gt; 999» / «&gt; 2,00 ГОм» — показание выше верхнего предела диапазона прибора.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>Измерения выполнил</t>
         </is>
       </c>
-      <c r="G68" s="14" t="inlineStr">
+      <c r="G72" s="14" t="inlineStr">
         <is>
           <t>инженер Андреев М.В. (III группа по ЭБ до 1000 В)</t>
         </is>
       </c>
-      <c r="K68" s="15" t="inlineStr">
+      <c r="K72" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>Протокол проверил</t>
         </is>
       </c>
-      <c r="G69" s="14" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности Иванчук М.В.</t>
         </is>
       </c>
-      <c r="K69" s="15" t="inlineStr">
+      <c r="K73" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>Присутствовал представитель лица, осуществляющего строительство</t>
         </is>
       </c>
-      <c r="G70" s="14" t="inlineStr">
+      <c r="G74" s="14" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="K70" s="15" t="inlineStr">
+      <c r="K74" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="16" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>ОБРАЗЕЦ</t>
         </is>
@@ -3319,32 +3541,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="K74:L74"/>
     <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A66:L66"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A12:L12"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A76:L76"/>
+    <mergeCell ref="G72:J72"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="K72:L72"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A72:L72"/>
-    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A68:F68"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A15:L15"/>
+    <mergeCell ref="K73:L73"/>
     <mergeCell ref="A11:L11"/>
-    <mergeCell ref="G69:J69"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="G74:J74"/>
     <mergeCell ref="A6:L6"/>
-    <mergeCell ref="G68:J68"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A65:L65"/>
+    <mergeCell ref="A70:L70"/>
+    <mergeCell ref="A69:L69"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3358,7 +3580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3427,7 +3649,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Исполнительная документация: 16/1/26-ИД-АБК, листы 2–3; кабельный журнал 16/1/26-ИД-АБК.КЖ (раздел СПС). Рабочая документация 16/1/26-АПС,СОУЭ-Р.</t>
+          <t>Исполнительная документация: 16/1/26-АПС,СОУЭ-ИД-АБК, листы 2–3; кабельный журнал 16/1/26-АПС,СОУЭ-ИД-АБК.КЖ. Рабочая документация 16/1/26-АПС,СОУЭ-Р.</t>
         </is>
       </c>
     </row>
@@ -4722,17 +4944,17 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>ДПЛС2.1</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>AU2</t>
+          <t>2BTH1.18,(40)</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>BIAD42\1.5Вт</t>
+          <t>2BTH1.25(60)</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -4742,20 +4964,20 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>1x2x1</t>
+          <t>1x2x0,5</t>
         </is>
       </c>
       <c r="G44" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I44" s="9" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr"/>
@@ -4766,17 +4988,17 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>ДПЛС2.1</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>BIAD42\1.5Вт</t>
+          <t>2BTH1.25(60)</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>BIAD41\3Вт</t>
+          <t>2BTH1.26(60)</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -4786,20 +5008,20 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>1x2x1</t>
+          <t>1x2x0,5</t>
         </is>
       </c>
       <c r="G45" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I45" s="9" t="inlineStr"/>
       <c r="J45" s="9" t="inlineStr"/>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr"/>
@@ -4810,17 +5032,17 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>ДПЛС2.1</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>BIAD41\3Вт</t>
+          <t>2BTH1.25(60)</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>BIAD38\1.5Вт</t>
+          <t>2BTH1.27(60)</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -4830,20 +5052,20 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>1x2x1</t>
+          <t>1x2x0,5</t>
         </is>
       </c>
       <c r="G46" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I46" s="9" t="inlineStr"/>
       <c r="J46" s="9" t="inlineStr"/>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr"/>
@@ -4854,17 +5076,17 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>ДПЛС2.1</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>BIAD38\1.5Вт</t>
+          <t>2BTH1.27(60)</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>BIAD43\1.5Вт</t>
+          <t>2BTH1.19,(40)</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
@@ -4874,20 +5096,20 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>1x2x1</t>
+          <t>1x2x0,5</t>
         </is>
       </c>
       <c r="G47" s="9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I47" s="9" t="inlineStr"/>
       <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr"/>
@@ -4903,12 +5125,12 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>BIAD43\1.5Вт</t>
+          <t>AU2</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>BIAD44\1.5Вт</t>
+          <t>BIAD42\1.5Вт</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -4922,7 +5144,7 @@
         </is>
       </c>
       <c r="G48" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H48" s="9" t="n">
         <v>500</v>
@@ -4947,12 +5169,12 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>BIAD44\1.5Вт</t>
+          <t>BIAD42\1.5Вт</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>BIAD39\3Вт</t>
+          <t>BIAD41\3Вт</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
@@ -4966,7 +5188,7 @@
         </is>
       </c>
       <c r="G49" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H49" s="9" t="n">
         <v>500</v>
@@ -4991,12 +5213,12 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>BIAD39\3Вт</t>
+          <t>BIAD41\3Вт</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>BIAD45\1.5Вт</t>
+          <t>BIAD38\1.5Вт</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -5010,7 +5232,7 @@
         </is>
       </c>
       <c r="G50" s="9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H50" s="9" t="n">
         <v>500</v>
@@ -5035,12 +5257,12 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>BIAD45\1.5Вт</t>
+          <t>BIAD38\1.5Вт</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>BIAD46\1.5Вт</t>
+          <t>BIAD43\1.5Вт</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
@@ -5054,7 +5276,7 @@
         </is>
       </c>
       <c r="G51" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H51" s="9" t="n">
         <v>500</v>
@@ -5079,12 +5301,12 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>BIAD46\1.5Вт</t>
+          <t>BIAD43\1.5Вт</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>BIAD40\3Вт</t>
+          <t>BIAD44\1.5Вт</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -5098,7 +5320,7 @@
         </is>
       </c>
       <c r="G52" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H52" s="9" t="n">
         <v>500</v>
@@ -5123,12 +5345,12 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>BIAD40\3Вт</t>
+          <t>BIAD44\1.5Вт</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>BIAD47\1.5Вт</t>
+          <t>BIAD39\3Вт</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
@@ -5142,7 +5364,7 @@
         </is>
       </c>
       <c r="G53" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H53" s="9" t="n">
         <v>500</v>
@@ -5167,12 +5389,12 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>BIAD47\1.5Вт</t>
+          <t>BIAD39\3Вт</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>BIAD48\1.5Вт</t>
+          <t>BIAD45\1.5Вт</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -5211,12 +5433,12 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>BIAD48\1.5Вт</t>
+          <t>BIAD45\1.5Вт</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>BIAD49\1.5Вт</t>
+          <t>BIAD46\1.5Вт</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -5255,12 +5477,12 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>BIAD49\1.5Вт</t>
+          <t>BIAD46\1.5Вт</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>BIAD50\1.5Вт</t>
+          <t>BIAD40\3Вт</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -5274,7 +5496,7 @@
         </is>
       </c>
       <c r="G56" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H56" s="9" t="n">
         <v>500</v>
@@ -5299,12 +5521,12 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>BIAD50\1.5Вт</t>
+          <t>BIAD40\3Вт</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>BIAD51\1.5Вт</t>
+          <t>BIAD47\1.5Вт</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -5343,12 +5565,12 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>BIAD51\1.5Вт</t>
+          <t>BIAD47\1.5Вт</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>BIAD52\1.5Вт</t>
+          <t>BIAD48\1.5Вт</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -5362,7 +5584,7 @@
         </is>
       </c>
       <c r="G58" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H58" s="9" t="n">
         <v>500</v>
@@ -5387,12 +5609,12 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>BIAD52\1.5Вт</t>
+          <t>BIAD48\1.5Вт</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>BIAD53\1.5Вт</t>
+          <t>BIAD49\1.5Вт</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -5406,7 +5628,7 @@
         </is>
       </c>
       <c r="G59" s="9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>500</v>
@@ -5431,12 +5653,12 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>BIAD53\1.5Вт</t>
+          <t>BIAD49\1.5Вт</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>BIAD54\1.5Вт</t>
+          <t>BIAD50\1.5Вт</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -5475,12 +5697,12 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>BIAD54\1.5Вт</t>
+          <t>BIAD50\1.5Вт</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>ST2</t>
+          <t>BIAD51\1.5Вт</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -5494,7 +5716,7 @@
         </is>
       </c>
       <c r="G61" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H61" s="9" t="n">
         <v>500</v>
@@ -5514,104 +5736,280 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>AU2</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>UR3</t>
+          <t>BIAD51\1.5Вт</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>AU2</t>
+          <t>BIAD52\1.5Вт</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>UTP-4P-Cat.5e</t>
+          <t>КПСнг(А)–FRHF</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>4х2х0.52</t>
+          <t>1x2x1</t>
         </is>
       </c>
       <c r="G62" s="9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="I62" s="9" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr"/>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr"/>
     </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>BIAD52\1.5Вт</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>BIAD53\1.5Вт</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>КПСнг(А)–FRHF</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>1x2x1</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr"/>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>BIAD53\1.5Вт</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>BIAD54\1.5Вт</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>КПСнг(А)–FRHF</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>1x2x1</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr"/>
+      <c r="J64" s="9" t="inlineStr"/>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>BIAD54\1.5Вт</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>ST2</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>КПСнг(А)–FRHF</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>1x2x1</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>AU2</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>UR3</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>AU2</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>UTP-4P-Cat.5e</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>4х2х0.52</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr"/>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr"/>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Заключение: ______________________________________________________________________________________________</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>Протокол распространяется только на испытанные линии. Запись «&gt; 999» / «&gt; 2,00 ГОм» — показание выше верхнего предела диапазона прибора.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>Измерения выполнил</t>
         </is>
       </c>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>инженер Андреев М.В. (III группа по ЭБ до 1000 В)</t>
         </is>
       </c>
-      <c r="K67" s="15" t="inlineStr">
+      <c r="K71" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>Протокол проверил</t>
         </is>
       </c>
-      <c r="G68" s="14" t="inlineStr">
+      <c r="G72" s="14" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности Иванчук М.В.</t>
         </is>
       </c>
-      <c r="K68" s="15" t="inlineStr">
+      <c r="K72" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>Присутствовал представитель лица, осуществляющего строительство</t>
         </is>
       </c>
-      <c r="G69" s="14" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="K69" s="15" t="inlineStr">
+      <c r="K73" s="15" t="inlineStr">
         <is>
           <t>__________</t>
         </is>
@@ -5619,30 +6017,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K68:L68"/>
     <mergeCell ref="A7:L7"/>
+    <mergeCell ref="G73:J73"/>
     <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A71:F71"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="G72:J72"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="K72:L72"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A14:L14"/>
-    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="G71:J71"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="K67:L67"/>
     <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A68:L68"/>
     <mergeCell ref="A13:L13"/>
+    <mergeCell ref="K71:L71"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="K73:L73"/>
     <mergeCell ref="A11:L11"/>
-    <mergeCell ref="G69:J69"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A6:L6"/>
-    <mergeCell ref="G68:J68"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A65:L65"/>
+    <mergeCell ref="A69:L69"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
